--- a/TOY01G.xlsx
+++ b/TOY01G.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="77">
   <si>
     <t/>
   </si>
@@ -634,17 +634,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,8 +664,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -680,11 +687,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -700,11 +707,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -720,11 +727,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -740,11 +747,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -760,11 +767,11 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -780,11 +787,11 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -800,11 +807,11 @@
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -820,11 +827,11 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -840,11 +847,11 @@
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -860,11 +867,11 @@
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -880,11 +887,11 @@
       <c r="E12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -900,11 +907,11 @@
       <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -920,11 +927,11 @@
       <c r="E14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -940,11 +947,11 @@
       <c r="E15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -960,11 +967,11 @@
       <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
@@ -980,11 +987,11 @@
       <c r="E17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
@@ -1000,11 +1007,11 @@
       <c r="E18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>47</v>
       </c>
@@ -1020,11 +1027,11 @@
       <c r="E19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
@@ -1040,11 +1047,11 @@
       <c r="E20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
@@ -1060,11 +1067,11 @@
       <c r="E21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>53</v>
       </c>
@@ -1080,11 +1087,11 @@
       <c r="E22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -1100,11 +1107,11 @@
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>57</v>
       </c>
@@ -1120,11 +1127,11 @@
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>59</v>
       </c>
@@ -1140,11 +1147,11 @@
       <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>61</v>
       </c>
@@ -1160,11 +1167,11 @@
       <c r="E26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H26" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -1180,11 +1187,11 @@
       <c r="E27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -1200,11 +1207,11 @@
       <c r="E28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H28" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>67</v>
       </c>
@@ -1220,11 +1227,11 @@
       <c r="E29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>69</v>
       </c>
@@ -1240,11 +1247,11 @@
       <c r="E30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>71</v>
       </c>
@@ -1260,11 +1267,11 @@
       <c r="E31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>73</v>
       </c>
@@ -1280,11 +1287,11 @@
       <c r="E32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H32" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>75</v>
       </c>
@@ -1300,7 +1307,7 @@
       <c r="E33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/TOY01G.xlsx
+++ b/TOY01G.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="77">
   <si>
     <t/>
   </si>
@@ -634,18 +634,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,14 +663,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -687,11 +680,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -707,11 +700,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -727,11 +720,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -747,11 +740,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -767,11 +760,11 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -787,11 +780,11 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -807,11 +800,11 @@
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -827,11 +820,11 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -847,11 +840,11 @@
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -867,11 +860,11 @@
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -887,11 +880,11 @@
       <c r="E12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -907,11 +900,11 @@
       <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -927,11 +920,11 @@
       <c r="E14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -947,11 +940,11 @@
       <c r="E15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -967,11 +960,11 @@
       <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
@@ -987,11 +980,11 @@
       <c r="E17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
@@ -1007,11 +1000,11 @@
       <c r="E18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>47</v>
       </c>
@@ -1027,11 +1020,11 @@
       <c r="E19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
@@ -1047,11 +1040,11 @@
       <c r="E20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
@@ -1067,11 +1060,11 @@
       <c r="E21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>53</v>
       </c>
@@ -1087,11 +1080,11 @@
       <c r="E22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -1107,11 +1100,11 @@
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>57</v>
       </c>
@@ -1127,11 +1120,11 @@
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>59</v>
       </c>
@@ -1147,11 +1140,11 @@
       <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>61</v>
       </c>
@@ -1167,11 +1160,11 @@
       <c r="E26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F26" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -1187,11 +1180,11 @@
       <c r="E27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -1207,11 +1200,11 @@
       <c r="E28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F28" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>67</v>
       </c>
@@ -1227,11 +1220,11 @@
       <c r="E29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>69</v>
       </c>
@@ -1247,11 +1240,11 @@
       <c r="E30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>71</v>
       </c>
@@ -1267,11 +1260,11 @@
       <c r="E31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>73</v>
       </c>
@@ -1287,11 +1280,11 @@
       <c r="E32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F32" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>75</v>
       </c>
@@ -1307,7 +1300,7 @@
       <c r="E33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>9</v>
       </c>
     </row>
